--- a/data/raw/Democracy in Action/review/dia_2016_organizations_review.xlsx
+++ b/data/raw/Democracy in Action/review/dia_2016_organizations_review.xlsx
@@ -9,17 +9,23 @@
     <sheet name="review" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review'!$A$1:$S$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review'!$A$1:$U$78</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="410">
   <si>
     <t xml:space="preserve">row_id</t>
   </si>
   <si>
+    <t xml:space="preserve">review_action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">review_note</t>
+  </si>
+  <si>
     <t xml:space="preserve">contest_id</t>
   </si>
   <si>
@@ -75,6 +81,9 @@
   </si>
   <si>
     <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">2016D</t>
@@ -1581,24 +1590,26 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="17.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="40.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="23.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="21.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="10.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="10.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="16.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="13.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="18.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="18.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="40.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="11.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="80.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="20.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="40.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="8.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="8.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="40.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="23.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="21.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="8.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="10.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="10.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="16.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="13.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="18.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="40.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="11.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="80.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="20.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1659,3622 +1670,4090 @@
       <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
       <c r="R2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J3" s="1"/>
-      <c r="K3" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
       <c r="R3" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J4" s="1"/>
-      <c r="K4" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
       <c r="R4" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J5" s="1"/>
-      <c r="K5" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
       <c r="R5" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J6" s="1"/>
-      <c r="K6" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
       <c r="R7" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
       <c r="R8" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J9" s="1"/>
-      <c r="K9" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
       <c r="R9" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J10" s="1"/>
-      <c r="K10" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
       <c r="R10" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J11" s="1"/>
-      <c r="K11" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
       <c r="R11" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J12" s="1"/>
-      <c r="K12" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
       <c r="R12" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J13" s="1"/>
-      <c r="K13" s="1" t="s">
-        <v>84</v>
-      </c>
+      <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
       <c r="R13" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J14" s="1"/>
-      <c r="K14" s="1" t="s">
-        <v>89</v>
-      </c>
+      <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
       <c r="R14" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J15" s="1"/>
-      <c r="K15" s="1" t="s">
-        <v>94</v>
-      </c>
+      <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
       <c r="R15" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J16" s="1"/>
-      <c r="K16" s="1" t="s">
-        <v>99</v>
-      </c>
+      <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
       <c r="R16" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J17" s="1"/>
-      <c r="K17" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
       <c r="R17" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>108</v>
+        <v>25</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J18" s="1"/>
-      <c r="K18" s="1" t="s">
-        <v>109</v>
-      </c>
+      <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
       <c r="R18" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>113</v>
+        <v>25</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J19" s="1"/>
-      <c r="K19" s="1" t="s">
-        <v>114</v>
-      </c>
+      <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1" t="s">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
       <c r="R19" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>118</v>
+        <v>25</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J20" s="1"/>
-      <c r="K20" s="1" t="s">
-        <v>119</v>
-      </c>
+      <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1" t="s">
-        <v>27</v>
+        <v>122</v>
       </c>
       <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
       <c r="R20" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>123</v>
+        <v>25</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J21" s="1"/>
-      <c r="K21" s="1" t="s">
-        <v>124</v>
-      </c>
+      <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1" t="s">
-        <v>27</v>
+        <v>127</v>
       </c>
       <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
       <c r="R21" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>128</v>
+        <v>25</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J22" s="1"/>
-      <c r="K22" s="1" t="s">
-        <v>129</v>
-      </c>
+      <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
       <c r="R22" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>133</v>
+        <v>25</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J23" s="1"/>
-      <c r="K23" s="1" t="s">
-        <v>134</v>
-      </c>
+      <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
       <c r="R23" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J24" s="1"/>
-      <c r="K24" s="1" t="s">
-        <v>139</v>
-      </c>
+      <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
       <c r="R24" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>143</v>
+        <v>25</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J25" s="1"/>
-      <c r="K25" s="1" t="s">
-        <v>144</v>
-      </c>
+      <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1" t="s">
-        <v>27</v>
+        <v>147</v>
       </c>
       <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
       <c r="R25" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>148</v>
+        <v>25</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J26" s="1"/>
-      <c r="K26" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1" t="s">
-        <v>27</v>
+        <v>152</v>
       </c>
       <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
       <c r="R26" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>153</v>
+        <v>25</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J27" s="1"/>
-      <c r="K27" s="1" t="s">
-        <v>154</v>
-      </c>
+      <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1" t="s">
-        <v>27</v>
+        <v>157</v>
       </c>
       <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
       <c r="R27" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>158</v>
+        <v>25</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J28" s="1"/>
-      <c r="K28" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1" t="s">
-        <v>27</v>
+        <v>162</v>
       </c>
       <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
       <c r="R28" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>163</v>
+        <v>25</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J29" s="1"/>
-      <c r="K29" s="1" t="s">
-        <v>164</v>
-      </c>
+      <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q29" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
       <c r="R29" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>168</v>
+        <v>25</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J30" s="1"/>
-      <c r="K30" s="1" t="s">
-        <v>169</v>
-      </c>
+      <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1" t="s">
-        <v>27</v>
+        <v>172</v>
       </c>
       <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
       <c r="R30" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J31" s="1"/>
-      <c r="K31" s="1" t="s">
-        <v>174</v>
-      </c>
+      <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
       <c r="R31" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>178</v>
+        <v>25</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J32" s="1"/>
-      <c r="K32" s="1" t="s">
-        <v>179</v>
-      </c>
+      <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
       <c r="R32" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>183</v>
+        <v>25</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J33" s="1"/>
-      <c r="K33" s="1" t="s">
-        <v>184</v>
-      </c>
+      <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>27</v>
+        <v>187</v>
       </c>
       <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
       <c r="R33" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>188</v>
+        <v>25</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J34" s="1"/>
-      <c r="K34" s="1" t="s">
-        <v>189</v>
-      </c>
+      <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1" t="s">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q34" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
       <c r="R34" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>193</v>
+        <v>25</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-      <c r="L35" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="P35" s="1"/>
-      <c r="Q35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>195</v>
-      </c>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
       <c r="S35" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>197</v>
+        <v>25</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J36" s="1"/>
-      <c r="K36" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q36" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
       <c r="R36" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-      <c r="K37" s="1" t="s">
-        <v>203</v>
-      </c>
+      <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
-        <v>27</v>
+        <v>206</v>
       </c>
       <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
       <c r="R37" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>207</v>
+        <v>25</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J38" s="1"/>
-      <c r="K38" s="1" t="s">
-        <v>208</v>
-      </c>
+      <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1" t="s">
-        <v>27</v>
+        <v>211</v>
       </c>
       <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q38" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
       <c r="R38" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T38" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="U38" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>212</v>
+        <v>25</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J39" s="1"/>
-      <c r="K39" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q39" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O39" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
       <c r="R39" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="U39" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>216</v>
+        <v>25</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J40" s="1"/>
-      <c r="K40" s="1" t="s">
-        <v>217</v>
-      </c>
+      <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1" t="s">
-        <v>27</v>
+        <v>220</v>
       </c>
       <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q40" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O40" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1"/>
       <c r="R40" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T40" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>221</v>
+        <v>25</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J41" s="1"/>
-      <c r="K41" s="1" t="s">
-        <v>222</v>
-      </c>
+      <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1" t="s">
-        <v>27</v>
+        <v>225</v>
       </c>
       <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q41" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O41" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1"/>
       <c r="R41" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T41" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>226</v>
+        <v>25</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J42" s="1"/>
-      <c r="K42" s="1" t="s">
-        <v>227</v>
-      </c>
+      <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1" t="s">
-        <v>27</v>
+        <v>230</v>
       </c>
       <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q42" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O42" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1"/>
       <c r="R42" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="U42" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>231</v>
+        <v>25</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J43" s="1"/>
-      <c r="K43" s="1" t="s">
-        <v>232</v>
-      </c>
+      <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1" t="s">
-        <v>27</v>
+        <v>235</v>
       </c>
       <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q43" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O43" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1"/>
       <c r="R43" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S43" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>236</v>
+        <v>25</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J44" s="1"/>
-      <c r="K44" s="1" t="s">
-        <v>237</v>
-      </c>
+      <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
-        <v>27</v>
+        <v>240</v>
       </c>
       <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q44" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O44" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1"/>
       <c r="R44" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="S44" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>241</v>
+        <v>25</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J45" s="1"/>
-      <c r="K45" s="1" t="s">
-        <v>99</v>
-      </c>
+      <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q45" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O45" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
       <c r="R45" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T45" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="U45" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>245</v>
+        <v>25</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J46" s="1"/>
-      <c r="K46" s="1" t="s">
-        <v>246</v>
-      </c>
+      <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="s">
-        <v>27</v>
+        <v>249</v>
       </c>
       <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q46" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O46" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P46" s="1"/>
+      <c r="Q46" s="1"/>
       <c r="R46" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="S46" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T46" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="U46" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J47" s="1"/>
-      <c r="K47" s="1" t="s">
-        <v>251</v>
-      </c>
+      <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1" t="s">
-        <v>27</v>
+        <v>254</v>
       </c>
       <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q47" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O47" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
       <c r="R47" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T47" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="U47" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>255</v>
+        <v>25</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J48" s="1"/>
-      <c r="K48" s="1" t="s">
-        <v>114</v>
-      </c>
+      <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1" t="s">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q48" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O48" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
       <c r="R48" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S48" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T48" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="U48" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>259</v>
+        <v>25</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J49" s="1"/>
-      <c r="K49" s="1" t="s">
-        <v>260</v>
-      </c>
+      <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1" t="s">
-        <v>27</v>
+        <v>263</v>
       </c>
       <c r="N49" s="1"/>
-      <c r="O49" s="1"/>
-      <c r="P49" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q49" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O49" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
       <c r="R49" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="S49" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T49" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="U49" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>264</v>
+        <v>25</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J50" s="1"/>
-      <c r="K50" s="1" t="s">
-        <v>265</v>
-      </c>
+      <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q50" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O50" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
       <c r="R50" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="S50" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T50" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="U50" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>269</v>
+        <v>25</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J51" s="1"/>
-      <c r="K51" s="1" t="s">
-        <v>265</v>
-      </c>
+      <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="N51" s="1"/>
-      <c r="O51" s="1"/>
-      <c r="P51" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q51" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O51" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
       <c r="R51" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="S51" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T51" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="U51" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>275</v>
+        <v>24</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
+        <v>278</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J52" s="1"/>
-      <c r="K52" s="1" t="s">
-        <v>277</v>
-      </c>
+      <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1" t="s">
-        <v>27</v>
+        <v>280</v>
       </c>
       <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q52" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O52" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
       <c r="R52" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="S52" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T52" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="U52" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>275</v>
+        <v>24</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
+        <v>278</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J53" s="1"/>
-      <c r="K53" s="1" t="s">
-        <v>282</v>
-      </c>
+      <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
-        <v>27</v>
+        <v>285</v>
       </c>
       <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
-      <c r="P53" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O53" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
       <c r="R53" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="S53" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T53" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="U53" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>275</v>
+        <v>24</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
+        <v>278</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J54" s="1"/>
-      <c r="K54" s="1" t="s">
-        <v>287</v>
-      </c>
+      <c r="K54" s="1"/>
       <c r="L54" s="1"/>
       <c r="M54" s="1" t="s">
-        <v>27</v>
+        <v>290</v>
       </c>
       <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O54" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="1"/>
       <c r="R54" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="S54" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T54" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="U54" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>275</v>
+        <v>24</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
+        <v>278</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J55" s="1"/>
-      <c r="K55" s="1" t="s">
-        <v>292</v>
-      </c>
+      <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1" t="s">
-        <v>27</v>
+        <v>295</v>
       </c>
       <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
-      <c r="P55" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O55" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
       <c r="R55" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="S55" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T55" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="U55" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>275</v>
+        <v>24</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
+        <v>278</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J56" s="1"/>
-      <c r="K56" s="1" t="s">
-        <v>297</v>
-      </c>
+      <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="s">
-        <v>27</v>
+        <v>300</v>
       </c>
       <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O56" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1"/>
       <c r="R56" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="S56" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T56" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="U56" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>275</v>
+        <v>24</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
+        <v>278</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J57" s="1"/>
-      <c r="K57" s="1" t="s">
-        <v>302</v>
-      </c>
+      <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1" t="s">
-        <v>27</v>
+        <v>305</v>
       </c>
       <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-      <c r="P57" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O57" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1"/>
       <c r="R57" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="S57" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="T57" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="U57" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>306</v>
+        <v>24</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>307</v>
+        <v>25</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
+        <v>309</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J58" s="1"/>
-      <c r="K58" s="1" t="s">
-        <v>308</v>
-      </c>
+      <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>27</v>
+        <v>311</v>
       </c>
       <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q58" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O58" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="1"/>
       <c r="R58" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="S58" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T58" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="U58" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>306</v>
+        <v>24</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>313</v>
+        <v>25</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
+        <v>309</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J59" s="1"/>
-      <c r="K59" s="1" t="s">
-        <v>314</v>
-      </c>
+      <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1" t="s">
-        <v>27</v>
+        <v>317</v>
       </c>
       <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
-      <c r="P59" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="Q59" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O59" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P59" s="1"/>
+      <c r="Q59" s="1"/>
       <c r="R59" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="S59" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T59" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="U59" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>306</v>
+        <v>24</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>318</v>
+        <v>25</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
+        <v>309</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J60" s="1"/>
-      <c r="K60" s="1" t="s">
-        <v>319</v>
-      </c>
+      <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1" t="s">
-        <v>27</v>
+        <v>322</v>
       </c>
       <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
-      <c r="P60" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="Q60" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O60" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1"/>
       <c r="R60" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="S60" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T60" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="U60" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>306</v>
+        <v>24</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>323</v>
+        <v>25</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
+        <v>309</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J61" s="1"/>
-      <c r="K61" s="1" t="s">
-        <v>324</v>
-      </c>
+      <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>27</v>
+        <v>327</v>
       </c>
       <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q61" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O61" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P61" s="1"/>
+      <c r="Q61" s="1"/>
       <c r="R61" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="S61" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T61" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="U61" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>306</v>
+        <v>24</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>328</v>
+        <v>25</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
+        <v>309</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J62" s="1"/>
-      <c r="K62" s="1" t="s">
-        <v>99</v>
-      </c>
+      <c r="K62" s="1"/>
       <c r="L62" s="1"/>
       <c r="M62" s="1" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q62" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O62" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P62" s="1"/>
+      <c r="Q62" s="1"/>
       <c r="R62" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="S62" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T62" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="U62" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>306</v>
+        <v>24</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>332</v>
+        <v>25</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
+        <v>309</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J63" s="1"/>
-      <c r="K63" s="1" t="s">
-        <v>333</v>
-      </c>
+      <c r="K63" s="1"/>
       <c r="L63" s="1"/>
       <c r="M63" s="1" t="s">
-        <v>27</v>
+        <v>336</v>
       </c>
       <c r="N63" s="1"/>
-      <c r="O63" s="1"/>
-      <c r="P63" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q63" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O63" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P63" s="1"/>
+      <c r="Q63" s="1"/>
       <c r="R63" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="S63" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T63" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="U63" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>306</v>
+        <v>24</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>337</v>
+        <v>25</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
+        <v>309</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J64" s="1"/>
-      <c r="K64" s="1" t="s">
-        <v>333</v>
-      </c>
+      <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1" t="s">
-        <v>27</v>
+        <v>336</v>
       </c>
       <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
-      <c r="P64" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="Q64" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O64" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P64" s="1"/>
+      <c r="Q64" s="1"/>
       <c r="R64" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S64" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T64" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="U64" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>306</v>
+        <v>24</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>202</v>
+        <v>25</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
+        <v>309</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J65" s="1"/>
-      <c r="K65" s="1" t="s">
-        <v>341</v>
-      </c>
+      <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1" t="s">
-        <v>27</v>
+        <v>344</v>
       </c>
       <c r="N65" s="1"/>
-      <c r="O65" s="1"/>
-      <c r="P65" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="Q65" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O65" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P65" s="1"/>
+      <c r="Q65" s="1"/>
       <c r="R65" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="S65" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T65" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="U65" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>306</v>
+        <v>24</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>345</v>
+        <v>25</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
+        <v>309</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J66" s="1"/>
-      <c r="K66" s="1" t="s">
-        <v>346</v>
-      </c>
+      <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1" t="s">
-        <v>27</v>
+        <v>349</v>
       </c>
       <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q66" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O66" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P66" s="1"/>
+      <c r="Q66" s="1"/>
       <c r="R66" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="S66" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T66" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="U66" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>306</v>
+        <v>24</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>350</v>
+        <v>25</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
+        <v>309</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J67" s="1"/>
-      <c r="K67" s="1" t="s">
-        <v>351</v>
-      </c>
+      <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1" t="s">
-        <v>27</v>
+        <v>354</v>
       </c>
       <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
-      <c r="P67" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="Q67" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O67" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P67" s="1"/>
+      <c r="Q67" s="1"/>
       <c r="R67" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="S67" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T67" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="U67" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>306</v>
+        <v>24</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>355</v>
+        <v>25</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
+        <v>309</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J68" s="1"/>
-      <c r="K68" s="1" t="s">
-        <v>356</v>
-      </c>
+      <c r="K68" s="1"/>
       <c r="L68" s="1"/>
       <c r="M68" s="1" t="s">
-        <v>27</v>
+        <v>359</v>
       </c>
       <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="Q68" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O68" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P68" s="1"/>
+      <c r="Q68" s="1"/>
       <c r="R68" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="S68" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T68" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="U68" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>306</v>
+        <v>24</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>360</v>
+        <v>25</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
+        <v>309</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J69" s="1"/>
-      <c r="K69" s="1" t="s">
-        <v>361</v>
-      </c>
+      <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="1" t="s">
-        <v>27</v>
+        <v>364</v>
       </c>
       <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
-      <c r="P69" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="Q69" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O69" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P69" s="1"/>
+      <c r="Q69" s="1"/>
       <c r="R69" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="S69" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T69" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="U69" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>365</v>
+        <v>24</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>366</v>
+        <v>277</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
+        <v>368</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J70" s="1"/>
-      <c r="K70" s="1" t="s">
-        <v>367</v>
-      </c>
+      <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="1" t="s">
-        <v>27</v>
+        <v>370</v>
       </c>
       <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
-      <c r="P70" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="Q70" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O70" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P70" s="1"/>
+      <c r="Q70" s="1"/>
       <c r="R70" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="S70" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T70" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="U70" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>365</v>
+        <v>24</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>371</v>
+        <v>277</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
+        <v>368</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J71" s="1"/>
-      <c r="K71" s="1" t="s">
-        <v>372</v>
-      </c>
+      <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1" t="s">
-        <v>27</v>
+        <v>375</v>
       </c>
       <c r="N71" s="1"/>
-      <c r="O71" s="1"/>
-      <c r="P71" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="Q71" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O71" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P71" s="1"/>
+      <c r="Q71" s="1"/>
       <c r="R71" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="S71" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T71" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="U71" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>365</v>
+        <v>24</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>376</v>
+        <v>277</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
+        <v>368</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J72" s="1"/>
-      <c r="K72" s="1" t="s">
-        <v>377</v>
-      </c>
+      <c r="K72" s="1"/>
       <c r="L72" s="1"/>
       <c r="M72" s="1" t="s">
-        <v>27</v>
+        <v>380</v>
       </c>
       <c r="N72" s="1"/>
-      <c r="O72" s="1"/>
-      <c r="P72" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="Q72" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O72" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P72" s="1"/>
+      <c r="Q72" s="1"/>
       <c r="R72" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="S72" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T72" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="U72" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>365</v>
+        <v>24</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
+        <v>368</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J73" s="1"/>
-      <c r="K73" s="1" t="s">
-        <v>381</v>
-      </c>
+      <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="1" t="s">
-        <v>27</v>
+        <v>384</v>
       </c>
       <c r="N73" s="1"/>
-      <c r="O73" s="1"/>
-      <c r="P73" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="Q73" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O73" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P73" s="1"/>
+      <c r="Q73" s="1"/>
       <c r="R73" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="S73" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T73" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="U73" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>365</v>
+        <v>24</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>385</v>
+        <v>277</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
+        <v>368</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J74" s="1"/>
-      <c r="K74" s="1" t="s">
-        <v>386</v>
-      </c>
+      <c r="K74" s="1"/>
       <c r="L74" s="1"/>
       <c r="M74" s="1" t="s">
-        <v>27</v>
+        <v>389</v>
       </c>
       <c r="N74" s="1"/>
-      <c r="O74" s="1"/>
-      <c r="P74" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="Q74" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O74" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P74" s="1"/>
+      <c r="Q74" s="1"/>
       <c r="R74" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="S74" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T74" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="U74" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>365</v>
+        <v>24</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>390</v>
+        <v>277</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
+        <v>368</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J75" s="1"/>
-      <c r="K75" s="1" t="s">
-        <v>391</v>
-      </c>
+      <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="1" t="s">
-        <v>27</v>
+        <v>394</v>
       </c>
       <c r="N75" s="1"/>
-      <c r="O75" s="1"/>
-      <c r="P75" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="Q75" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O75" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P75" s="1"/>
+      <c r="Q75" s="1"/>
       <c r="R75" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="S75" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T75" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="U75" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>365</v>
+        <v>24</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>395</v>
+        <v>277</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
+        <v>368</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J76" s="1"/>
-      <c r="K76" s="1" t="s">
-        <v>396</v>
-      </c>
+      <c r="K76" s="1"/>
       <c r="L76" s="1"/>
       <c r="M76" s="1" t="s">
-        <v>27</v>
+        <v>399</v>
       </c>
       <c r="N76" s="1"/>
-      <c r="O76" s="1"/>
-      <c r="P76" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="Q76" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O76" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P76" s="1"/>
+      <c r="Q76" s="1"/>
       <c r="R76" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="S76" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T76" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="U76" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>400</v>
+        <v>24</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
+        <v>403</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J77" s="1"/>
-      <c r="K77" s="1" t="s">
-        <v>227</v>
-      </c>
+      <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="1" t="s">
-        <v>27</v>
+        <v>230</v>
       </c>
       <c r="N77" s="1"/>
-      <c r="O77" s="1"/>
-      <c r="P77" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="Q77" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O77" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P77" s="1"/>
+      <c r="Q77" s="1"/>
       <c r="R77" s="1" t="s">
-        <v>229</v>
+        <v>404</v>
       </c>
       <c r="S77" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T77" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="U77" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>403</v>
+        <v>24</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>404</v>
+        <v>277</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
+        <v>406</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="J78" s="1"/>
-      <c r="K78" s="1" t="s">
-        <v>99</v>
-      </c>
+      <c r="K78" s="1"/>
       <c r="L78" s="1"/>
       <c r="M78" s="1" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N78" s="1"/>
-      <c r="O78" s="1"/>
-      <c r="P78" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="Q78" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O78" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P78" s="1"/>
+      <c r="Q78" s="1"/>
       <c r="R78" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="S78" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="T78" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="U78" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="79">
@@ -5297,6 +5776,8 @@
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
+      <c r="T79" s="1"/>
+      <c r="U79" s="1"/>
     </row>
     <row r="80">
       <c r="A80" s="1"/>
@@ -5318,6 +5799,8 @@
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
+      <c r="T80" s="1"/>
+      <c r="U80" s="1"/>
     </row>
     <row r="81">
       <c r="A81" s="1"/>
@@ -5339,6 +5822,8 @@
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
+      <c r="T81" s="1"/>
+      <c r="U81" s="1"/>
     </row>
     <row r="82">
       <c r="A82" s="1"/>
@@ -5360,6 +5845,8 @@
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
+      <c r="T82" s="1"/>
+      <c r="U82" s="1"/>
     </row>
     <row r="83">
       <c r="A83" s="1"/>
@@ -5381,6 +5868,8 @@
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
+      <c r="T83" s="1"/>
+      <c r="U83" s="1"/>
     </row>
     <row r="84">
       <c r="A84" s="1"/>
@@ -5402,6 +5891,8 @@
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
+      <c r="T84" s="1"/>
+      <c r="U84" s="1"/>
     </row>
     <row r="85">
       <c r="A85" s="1"/>
@@ -5423,6 +5914,8 @@
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
+      <c r="T85" s="1"/>
+      <c r="U85" s="1"/>
     </row>
     <row r="86">
       <c r="A86" s="1"/>
@@ -5444,6 +5937,8 @@
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
+      <c r="T86" s="1"/>
+      <c r="U86" s="1"/>
     </row>
     <row r="87">
       <c r="A87" s="1"/>
@@ -5465,6 +5960,8 @@
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
+      <c r="T87" s="1"/>
+      <c r="U87" s="1"/>
     </row>
     <row r="88">
       <c r="A88" s="1"/>
@@ -5486,6 +5983,8 @@
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
+      <c r="T88" s="1"/>
+      <c r="U88" s="1"/>
     </row>
     <row r="89">
       <c r="A89" s="1"/>
@@ -5507,6 +6006,8 @@
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
+      <c r="T89" s="1"/>
+      <c r="U89" s="1"/>
     </row>
     <row r="90">
       <c r="A90" s="1"/>
@@ -5528,6 +6029,8 @@
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
+      <c r="T90" s="1"/>
+      <c r="U90" s="1"/>
     </row>
     <row r="91">
       <c r="A91" s="1"/>
@@ -5549,6 +6052,8 @@
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
+      <c r="T91" s="1"/>
+      <c r="U91" s="1"/>
     </row>
     <row r="92">
       <c r="A92" s="1"/>
@@ -5570,6 +6075,8 @@
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
+      <c r="T92" s="1"/>
+      <c r="U92" s="1"/>
     </row>
     <row r="93">
       <c r="A93" s="1"/>
@@ -5591,6 +6098,8 @@
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
+      <c r="T93" s="1"/>
+      <c r="U93" s="1"/>
     </row>
     <row r="94">
       <c r="A94" s="1"/>
@@ -5612,6 +6121,8 @@
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
+      <c r="T94" s="1"/>
+      <c r="U94" s="1"/>
     </row>
     <row r="95">
       <c r="A95" s="1"/>
@@ -5633,6 +6144,8 @@
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
+      <c r="T95" s="1"/>
+      <c r="U95" s="1"/>
     </row>
     <row r="96">
       <c r="A96" s="1"/>
@@ -5654,6 +6167,8 @@
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
+      <c r="T96" s="1"/>
+      <c r="U96" s="1"/>
     </row>
     <row r="97">
       <c r="A97" s="1"/>
@@ -5675,6 +6190,8 @@
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
       <c r="S97" s="1"/>
+      <c r="T97" s="1"/>
+      <c r="U97" s="1"/>
     </row>
     <row r="98">
       <c r="A98" s="1"/>
@@ -5696,6 +6213,8 @@
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
       <c r="S98" s="1"/>
+      <c r="T98" s="1"/>
+      <c r="U98" s="1"/>
     </row>
     <row r="99">
       <c r="A99" s="1"/>
@@ -5717,6 +6236,8 @@
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
       <c r="S99" s="1"/>
+      <c r="T99" s="1"/>
+      <c r="U99" s="1"/>
     </row>
     <row r="100">
       <c r="A100" s="1"/>
@@ -5738,6 +6259,8 @@
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
       <c r="S100" s="1"/>
+      <c r="T100" s="1"/>
+      <c r="U100" s="1"/>
     </row>
     <row r="101">
       <c r="A101" s="1"/>
@@ -5759,6 +6282,8 @@
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
       <c r="S101" s="1"/>
+      <c r="T101" s="1"/>
+      <c r="U101" s="1"/>
     </row>
     <row r="102">
       <c r="A102" s="1"/>
@@ -5780,6 +6305,8 @@
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
       <c r="S102" s="1"/>
+      <c r="T102" s="1"/>
+      <c r="U102" s="1"/>
     </row>
     <row r="103">
       <c r="A103" s="1"/>
@@ -5801,6 +6328,8 @@
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
       <c r="S103" s="1"/>
+      <c r="T103" s="1"/>
+      <c r="U103" s="1"/>
     </row>
     <row r="104">
       <c r="A104" s="1"/>
@@ -5822,6 +6351,8 @@
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
       <c r="S104" s="1"/>
+      <c r="T104" s="1"/>
+      <c r="U104" s="1"/>
     </row>
     <row r="105">
       <c r="A105" s="1"/>
@@ -5843,6 +6374,8 @@
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
       <c r="S105" s="1"/>
+      <c r="T105" s="1"/>
+      <c r="U105" s="1"/>
     </row>
     <row r="106">
       <c r="A106" s="1"/>
@@ -5864,6 +6397,8 @@
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
       <c r="S106" s="1"/>
+      <c r="T106" s="1"/>
+      <c r="U106" s="1"/>
     </row>
     <row r="107">
       <c r="A107" s="1"/>
@@ -5885,6 +6420,8 @@
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
       <c r="S107" s="1"/>
+      <c r="T107" s="1"/>
+      <c r="U107" s="1"/>
     </row>
     <row r="108">
       <c r="A108" s="1"/>
@@ -5906,6 +6443,8 @@
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
       <c r="S108" s="1"/>
+      <c r="T108" s="1"/>
+      <c r="U108" s="1"/>
     </row>
     <row r="109">
       <c r="A109" s="1"/>
@@ -5927,6 +6466,8 @@
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
       <c r="S109" s="1"/>
+      <c r="T109" s="1"/>
+      <c r="U109" s="1"/>
     </row>
     <row r="110">
       <c r="A110" s="1"/>
@@ -5948,6 +6489,8 @@
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
       <c r="S110" s="1"/>
+      <c r="T110" s="1"/>
+      <c r="U110" s="1"/>
     </row>
     <row r="111">
       <c r="A111" s="1"/>
@@ -5969,6 +6512,8 @@
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
       <c r="S111" s="1"/>
+      <c r="T111" s="1"/>
+      <c r="U111" s="1"/>
     </row>
     <row r="112">
       <c r="A112" s="1"/>
@@ -5990,6 +6535,8 @@
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
       <c r="S112" s="1"/>
+      <c r="T112" s="1"/>
+      <c r="U112" s="1"/>
     </row>
     <row r="113">
       <c r="A113" s="1"/>
@@ -6011,6 +6558,8 @@
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
       <c r="S113" s="1"/>
+      <c r="T113" s="1"/>
+      <c r="U113" s="1"/>
     </row>
     <row r="114">
       <c r="A114" s="1"/>
@@ -6032,6 +6581,8 @@
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
       <c r="S114" s="1"/>
+      <c r="T114" s="1"/>
+      <c r="U114" s="1"/>
     </row>
     <row r="115">
       <c r="A115" s="1"/>
@@ -6053,6 +6604,8 @@
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
       <c r="S115" s="1"/>
+      <c r="T115" s="1"/>
+      <c r="U115" s="1"/>
     </row>
     <row r="116">
       <c r="A116" s="1"/>
@@ -6074,6 +6627,8 @@
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
       <c r="S116" s="1"/>
+      <c r="T116" s="1"/>
+      <c r="U116" s="1"/>
     </row>
     <row r="117">
       <c r="A117" s="1"/>
@@ -6095,6 +6650,8 @@
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
       <c r="S117" s="1"/>
+      <c r="T117" s="1"/>
+      <c r="U117" s="1"/>
     </row>
     <row r="118">
       <c r="A118" s="1"/>
@@ -6116,6 +6673,8 @@
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
       <c r="S118" s="1"/>
+      <c r="T118" s="1"/>
+      <c r="U118" s="1"/>
     </row>
     <row r="119">
       <c r="A119" s="1"/>
@@ -6137,6 +6696,8 @@
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
       <c r="S119" s="1"/>
+      <c r="T119" s="1"/>
+      <c r="U119" s="1"/>
     </row>
     <row r="120">
       <c r="A120" s="1"/>
@@ -6158,6 +6719,8 @@
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
       <c r="S120" s="1"/>
+      <c r="T120" s="1"/>
+      <c r="U120" s="1"/>
     </row>
     <row r="121">
       <c r="A121" s="1"/>
@@ -6179,6 +6742,8 @@
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
       <c r="S121" s="1"/>
+      <c r="T121" s="1"/>
+      <c r="U121" s="1"/>
     </row>
     <row r="122">
       <c r="A122" s="1"/>
@@ -6200,6 +6765,8 @@
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
       <c r="S122" s="1"/>
+      <c r="T122" s="1"/>
+      <c r="U122" s="1"/>
     </row>
     <row r="123">
       <c r="A123" s="1"/>
@@ -6221,6 +6788,8 @@
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
       <c r="S123" s="1"/>
+      <c r="T123" s="1"/>
+      <c r="U123" s="1"/>
     </row>
     <row r="124">
       <c r="A124" s="1"/>
@@ -6242,6 +6811,8 @@
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
       <c r="S124" s="1"/>
+      <c r="T124" s="1"/>
+      <c r="U124" s="1"/>
     </row>
     <row r="125">
       <c r="A125" s="1"/>
@@ -6263,6 +6834,8 @@
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
       <c r="S125" s="1"/>
+      <c r="T125" s="1"/>
+      <c r="U125" s="1"/>
     </row>
     <row r="126">
       <c r="A126" s="1"/>
@@ -6284,6 +6857,8 @@
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
       <c r="S126" s="1"/>
+      <c r="T126" s="1"/>
+      <c r="U126" s="1"/>
     </row>
     <row r="127">
       <c r="A127" s="1"/>
@@ -6305,6 +6880,8 @@
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
       <c r="S127" s="1"/>
+      <c r="T127" s="1"/>
+      <c r="U127" s="1"/>
     </row>
     <row r="128">
       <c r="A128" s="1"/>
@@ -6326,6 +6903,8 @@
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
       <c r="S128" s="1"/>
+      <c r="T128" s="1"/>
+      <c r="U128" s="1"/>
     </row>
     <row r="129">
       <c r="A129" s="1"/>
@@ -6347,6 +6926,8 @@
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
       <c r="S129" s="1"/>
+      <c r="T129" s="1"/>
+      <c r="U129" s="1"/>
     </row>
     <row r="130">
       <c r="A130" s="1"/>
@@ -6368,6 +6949,8 @@
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
+      <c r="T130" s="1"/>
+      <c r="U130" s="1"/>
     </row>
     <row r="131">
       <c r="A131" s="1"/>
@@ -6389,6 +6972,8 @@
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
       <c r="S131" s="1"/>
+      <c r="T131" s="1"/>
+      <c r="U131" s="1"/>
     </row>
     <row r="132">
       <c r="A132" s="1"/>
@@ -6410,6 +6995,8 @@
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
       <c r="S132" s="1"/>
+      <c r="T132" s="1"/>
+      <c r="U132" s="1"/>
     </row>
     <row r="133">
       <c r="A133" s="1"/>
@@ -6431,6 +7018,8 @@
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
+      <c r="T133" s="1"/>
+      <c r="U133" s="1"/>
     </row>
     <row r="134">
       <c r="A134" s="1"/>
@@ -6452,6 +7041,8 @@
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
       <c r="S134" s="1"/>
+      <c r="T134" s="1"/>
+      <c r="U134" s="1"/>
     </row>
     <row r="135">
       <c r="A135" s="1"/>
@@ -6473,6 +7064,8 @@
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
       <c r="S135" s="1"/>
+      <c r="T135" s="1"/>
+      <c r="U135" s="1"/>
     </row>
     <row r="136">
       <c r="A136" s="1"/>
@@ -6494,6 +7087,8 @@
       <c r="Q136" s="1"/>
       <c r="R136" s="1"/>
       <c r="S136" s="1"/>
+      <c r="T136" s="1"/>
+      <c r="U136" s="1"/>
     </row>
     <row r="137">
       <c r="A137" s="1"/>
@@ -6515,6 +7110,8 @@
       <c r="Q137" s="1"/>
       <c r="R137" s="1"/>
       <c r="S137" s="1"/>
+      <c r="T137" s="1"/>
+      <c r="U137" s="1"/>
     </row>
     <row r="138">
       <c r="A138" s="1"/>
@@ -6536,6 +7133,8 @@
       <c r="Q138" s="1"/>
       <c r="R138" s="1"/>
       <c r="S138" s="1"/>
+      <c r="T138" s="1"/>
+      <c r="U138" s="1"/>
     </row>
     <row r="139">
       <c r="A139" s="1"/>
@@ -6557,6 +7156,8 @@
       <c r="Q139" s="1"/>
       <c r="R139" s="1"/>
       <c r="S139" s="1"/>
+      <c r="T139" s="1"/>
+      <c r="U139" s="1"/>
     </row>
     <row r="140">
       <c r="A140" s="1"/>
@@ -6578,6 +7179,8 @@
       <c r="Q140" s="1"/>
       <c r="R140" s="1"/>
       <c r="S140" s="1"/>
+      <c r="T140" s="1"/>
+      <c r="U140" s="1"/>
     </row>
     <row r="141">
       <c r="A141" s="1"/>
@@ -6599,6 +7202,8 @@
       <c r="Q141" s="1"/>
       <c r="R141" s="1"/>
       <c r="S141" s="1"/>
+      <c r="T141" s="1"/>
+      <c r="U141" s="1"/>
     </row>
     <row r="142">
       <c r="A142" s="1"/>
@@ -6620,6 +7225,8 @@
       <c r="Q142" s="1"/>
       <c r="R142" s="1"/>
       <c r="S142" s="1"/>
+      <c r="T142" s="1"/>
+      <c r="U142" s="1"/>
     </row>
     <row r="143">
       <c r="A143" s="1"/>
@@ -6641,6 +7248,8 @@
       <c r="Q143" s="1"/>
       <c r="R143" s="1"/>
       <c r="S143" s="1"/>
+      <c r="T143" s="1"/>
+      <c r="U143" s="1"/>
     </row>
     <row r="144">
       <c r="A144" s="1"/>
@@ -6662,6 +7271,8 @@
       <c r="Q144" s="1"/>
       <c r="R144" s="1"/>
       <c r="S144" s="1"/>
+      <c r="T144" s="1"/>
+      <c r="U144" s="1"/>
     </row>
     <row r="145">
       <c r="A145" s="1"/>
@@ -6683,6 +7294,8 @@
       <c r="Q145" s="1"/>
       <c r="R145" s="1"/>
       <c r="S145" s="1"/>
+      <c r="T145" s="1"/>
+      <c r="U145" s="1"/>
     </row>
     <row r="146">
       <c r="A146" s="1"/>
@@ -6704,6 +7317,8 @@
       <c r="Q146" s="1"/>
       <c r="R146" s="1"/>
       <c r="S146" s="1"/>
+      <c r="T146" s="1"/>
+      <c r="U146" s="1"/>
     </row>
     <row r="147">
       <c r="A147" s="1"/>
@@ -6725,6 +7340,8 @@
       <c r="Q147" s="1"/>
       <c r="R147" s="1"/>
       <c r="S147" s="1"/>
+      <c r="T147" s="1"/>
+      <c r="U147" s="1"/>
     </row>
     <row r="148">
       <c r="A148" s="1"/>
@@ -6746,6 +7363,8 @@
       <c r="Q148" s="1"/>
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
+      <c r="T148" s="1"/>
+      <c r="U148" s="1"/>
     </row>
     <row r="149">
       <c r="A149" s="1"/>
@@ -6767,6 +7386,8 @@
       <c r="Q149" s="1"/>
       <c r="R149" s="1"/>
       <c r="S149" s="1"/>
+      <c r="T149" s="1"/>
+      <c r="U149" s="1"/>
     </row>
     <row r="150">
       <c r="A150" s="1"/>
@@ -6788,6 +7409,8 @@
       <c r="Q150" s="1"/>
       <c r="R150" s="1"/>
       <c r="S150" s="1"/>
+      <c r="T150" s="1"/>
+      <c r="U150" s="1"/>
     </row>
     <row r="151">
       <c r="A151" s="1"/>
@@ -6809,6 +7432,8 @@
       <c r="Q151" s="1"/>
       <c r="R151" s="1"/>
       <c r="S151" s="1"/>
+      <c r="T151" s="1"/>
+      <c r="U151" s="1"/>
     </row>
     <row r="152">
       <c r="A152" s="1"/>
@@ -6830,6 +7455,8 @@
       <c r="Q152" s="1"/>
       <c r="R152" s="1"/>
       <c r="S152" s="1"/>
+      <c r="T152" s="1"/>
+      <c r="U152" s="1"/>
     </row>
     <row r="153">
       <c r="A153" s="1"/>
@@ -6851,6 +7478,8 @@
       <c r="Q153" s="1"/>
       <c r="R153" s="1"/>
       <c r="S153" s="1"/>
+      <c r="T153" s="1"/>
+      <c r="U153" s="1"/>
     </row>
     <row r="154">
       <c r="A154" s="1"/>
@@ -6872,6 +7501,8 @@
       <c r="Q154" s="1"/>
       <c r="R154" s="1"/>
       <c r="S154" s="1"/>
+      <c r="T154" s="1"/>
+      <c r="U154" s="1"/>
     </row>
     <row r="155">
       <c r="A155" s="1"/>
@@ -6893,6 +7524,8 @@
       <c r="Q155" s="1"/>
       <c r="R155" s="1"/>
       <c r="S155" s="1"/>
+      <c r="T155" s="1"/>
+      <c r="U155" s="1"/>
     </row>
     <row r="156">
       <c r="A156" s="1"/>
@@ -6914,6 +7547,8 @@
       <c r="Q156" s="1"/>
       <c r="R156" s="1"/>
       <c r="S156" s="1"/>
+      <c r="T156" s="1"/>
+      <c r="U156" s="1"/>
     </row>
     <row r="157">
       <c r="A157" s="1"/>
@@ -6935,6 +7570,8 @@
       <c r="Q157" s="1"/>
       <c r="R157" s="1"/>
       <c r="S157" s="1"/>
+      <c r="T157" s="1"/>
+      <c r="U157" s="1"/>
     </row>
     <row r="158">
       <c r="A158" s="1"/>
@@ -6956,6 +7593,8 @@
       <c r="Q158" s="1"/>
       <c r="R158" s="1"/>
       <c r="S158" s="1"/>
+      <c r="T158" s="1"/>
+      <c r="U158" s="1"/>
     </row>
     <row r="159">
       <c r="A159" s="1"/>
@@ -6977,6 +7616,8 @@
       <c r="Q159" s="1"/>
       <c r="R159" s="1"/>
       <c r="S159" s="1"/>
+      <c r="T159" s="1"/>
+      <c r="U159" s="1"/>
     </row>
     <row r="160">
       <c r="A160" s="1"/>
@@ -6998,6 +7639,8 @@
       <c r="Q160" s="1"/>
       <c r="R160" s="1"/>
       <c r="S160" s="1"/>
+      <c r="T160" s="1"/>
+      <c r="U160" s="1"/>
     </row>
     <row r="161">
       <c r="A161" s="1"/>
@@ -7019,6 +7662,8 @@
       <c r="Q161" s="1"/>
       <c r="R161" s="1"/>
       <c r="S161" s="1"/>
+      <c r="T161" s="1"/>
+      <c r="U161" s="1"/>
     </row>
     <row r="162">
       <c r="A162" s="1"/>
@@ -7040,6 +7685,8 @@
       <c r="Q162" s="1"/>
       <c r="R162" s="1"/>
       <c r="S162" s="1"/>
+      <c r="T162" s="1"/>
+      <c r="U162" s="1"/>
     </row>
     <row r="163">
       <c r="A163" s="1"/>
@@ -7061,6 +7708,8 @@
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
       <c r="S163" s="1"/>
+      <c r="T163" s="1"/>
+      <c r="U163" s="1"/>
     </row>
     <row r="164">
       <c r="A164" s="1"/>
@@ -7082,6 +7731,8 @@
       <c r="Q164" s="1"/>
       <c r="R164" s="1"/>
       <c r="S164" s="1"/>
+      <c r="T164" s="1"/>
+      <c r="U164" s="1"/>
     </row>
     <row r="165">
       <c r="A165" s="1"/>
@@ -7103,6 +7754,8 @@
       <c r="Q165" s="1"/>
       <c r="R165" s="1"/>
       <c r="S165" s="1"/>
+      <c r="T165" s="1"/>
+      <c r="U165" s="1"/>
     </row>
     <row r="166">
       <c r="A166" s="1"/>
@@ -7124,6 +7777,8 @@
       <c r="Q166" s="1"/>
       <c r="R166" s="1"/>
       <c r="S166" s="1"/>
+      <c r="T166" s="1"/>
+      <c r="U166" s="1"/>
     </row>
     <row r="167">
       <c r="A167" s="1"/>
@@ -7145,6 +7800,8 @@
       <c r="Q167" s="1"/>
       <c r="R167" s="1"/>
       <c r="S167" s="1"/>
+      <c r="T167" s="1"/>
+      <c r="U167" s="1"/>
     </row>
     <row r="168">
       <c r="A168" s="1"/>
@@ -7166,6 +7823,8 @@
       <c r="Q168" s="1"/>
       <c r="R168" s="1"/>
       <c r="S168" s="1"/>
+      <c r="T168" s="1"/>
+      <c r="U168" s="1"/>
     </row>
     <row r="169">
       <c r="A169" s="1"/>
@@ -7187,6 +7846,8 @@
       <c r="Q169" s="1"/>
       <c r="R169" s="1"/>
       <c r="S169" s="1"/>
+      <c r="T169" s="1"/>
+      <c r="U169" s="1"/>
     </row>
     <row r="170">
       <c r="A170" s="1"/>
@@ -7208,6 +7869,8 @@
       <c r="Q170" s="1"/>
       <c r="R170" s="1"/>
       <c r="S170" s="1"/>
+      <c r="T170" s="1"/>
+      <c r="U170" s="1"/>
     </row>
     <row r="171">
       <c r="A171" s="1"/>
@@ -7229,6 +7892,8 @@
       <c r="Q171" s="1"/>
       <c r="R171" s="1"/>
       <c r="S171" s="1"/>
+      <c r="T171" s="1"/>
+      <c r="U171" s="1"/>
     </row>
     <row r="172">
       <c r="A172" s="1"/>
@@ -7250,6 +7915,8 @@
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
       <c r="S172" s="1"/>
+      <c r="T172" s="1"/>
+      <c r="U172" s="1"/>
     </row>
     <row r="173">
       <c r="A173" s="1"/>
@@ -7271,6 +7938,8 @@
       <c r="Q173" s="1"/>
       <c r="R173" s="1"/>
       <c r="S173" s="1"/>
+      <c r="T173" s="1"/>
+      <c r="U173" s="1"/>
     </row>
     <row r="174">
       <c r="A174" s="1"/>
@@ -7292,6 +7961,8 @@
       <c r="Q174" s="1"/>
       <c r="R174" s="1"/>
       <c r="S174" s="1"/>
+      <c r="T174" s="1"/>
+      <c r="U174" s="1"/>
     </row>
     <row r="175">
       <c r="A175" s="1"/>
@@ -7313,6 +7984,8 @@
       <c r="Q175" s="1"/>
       <c r="R175" s="1"/>
       <c r="S175" s="1"/>
+      <c r="T175" s="1"/>
+      <c r="U175" s="1"/>
     </row>
     <row r="176">
       <c r="A176" s="1"/>
@@ -7334,6 +8007,8 @@
       <c r="Q176" s="1"/>
       <c r="R176" s="1"/>
       <c r="S176" s="1"/>
+      <c r="T176" s="1"/>
+      <c r="U176" s="1"/>
     </row>
     <row r="177">
       <c r="A177" s="1"/>
@@ -7355,6 +8030,8 @@
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
       <c r="S177" s="1"/>
+      <c r="T177" s="1"/>
+      <c r="U177" s="1"/>
     </row>
     <row r="178">
       <c r="A178" s="1"/>
@@ -7376,6 +8053,8 @@
       <c r="Q178" s="1"/>
       <c r="R178" s="1"/>
       <c r="S178" s="1"/>
+      <c r="T178" s="1"/>
+      <c r="U178" s="1"/>
     </row>
     <row r="179">
       <c r="A179" s="1"/>
@@ -7397,6 +8076,8 @@
       <c r="Q179" s="1"/>
       <c r="R179" s="1"/>
       <c r="S179" s="1"/>
+      <c r="T179" s="1"/>
+      <c r="U179" s="1"/>
     </row>
     <row r="180">
       <c r="A180" s="1"/>
@@ -7418,6 +8099,8 @@
       <c r="Q180" s="1"/>
       <c r="R180" s="1"/>
       <c r="S180" s="1"/>
+      <c r="T180" s="1"/>
+      <c r="U180" s="1"/>
     </row>
     <row r="181">
       <c r="A181" s="1"/>
@@ -7439,6 +8122,8 @@
       <c r="Q181" s="1"/>
       <c r="R181" s="1"/>
       <c r="S181" s="1"/>
+      <c r="T181" s="1"/>
+      <c r="U181" s="1"/>
     </row>
     <row r="182">
       <c r="A182" s="1"/>
@@ -7460,6 +8145,8 @@
       <c r="Q182" s="1"/>
       <c r="R182" s="1"/>
       <c r="S182" s="1"/>
+      <c r="T182" s="1"/>
+      <c r="U182" s="1"/>
     </row>
     <row r="183">
       <c r="A183" s="1"/>
@@ -7481,6 +8168,8 @@
       <c r="Q183" s="1"/>
       <c r="R183" s="1"/>
       <c r="S183" s="1"/>
+      <c r="T183" s="1"/>
+      <c r="U183" s="1"/>
     </row>
     <row r="184">
       <c r="A184" s="1"/>
@@ -7502,6 +8191,8 @@
       <c r="Q184" s="1"/>
       <c r="R184" s="1"/>
       <c r="S184" s="1"/>
+      <c r="T184" s="1"/>
+      <c r="U184" s="1"/>
     </row>
     <row r="185">
       <c r="A185" s="1"/>
@@ -7523,6 +8214,8 @@
       <c r="Q185" s="1"/>
       <c r="R185" s="1"/>
       <c r="S185" s="1"/>
+      <c r="T185" s="1"/>
+      <c r="U185" s="1"/>
     </row>
     <row r="186">
       <c r="A186" s="1"/>
@@ -7544,6 +8237,8 @@
       <c r="Q186" s="1"/>
       <c r="R186" s="1"/>
       <c r="S186" s="1"/>
+      <c r="T186" s="1"/>
+      <c r="U186" s="1"/>
     </row>
     <row r="187">
       <c r="A187" s="1"/>
@@ -7565,6 +8260,8 @@
       <c r="Q187" s="1"/>
       <c r="R187" s="1"/>
       <c r="S187" s="1"/>
+      <c r="T187" s="1"/>
+      <c r="U187" s="1"/>
     </row>
     <row r="188">
       <c r="A188" s="1"/>
@@ -7586,6 +8283,8 @@
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
       <c r="S188" s="1"/>
+      <c r="T188" s="1"/>
+      <c r="U188" s="1"/>
     </row>
     <row r="189">
       <c r="A189" s="1"/>
@@ -7607,6 +8306,8 @@
       <c r="Q189" s="1"/>
       <c r="R189" s="1"/>
       <c r="S189" s="1"/>
+      <c r="T189" s="1"/>
+      <c r="U189" s="1"/>
     </row>
     <row r="190">
       <c r="A190" s="1"/>
@@ -7628,6 +8329,8 @@
       <c r="Q190" s="1"/>
       <c r="R190" s="1"/>
       <c r="S190" s="1"/>
+      <c r="T190" s="1"/>
+      <c r="U190" s="1"/>
     </row>
     <row r="191">
       <c r="A191" s="1"/>
@@ -7649,6 +8352,8 @@
       <c r="Q191" s="1"/>
       <c r="R191" s="1"/>
       <c r="S191" s="1"/>
+      <c r="T191" s="1"/>
+      <c r="U191" s="1"/>
     </row>
     <row r="192">
       <c r="A192" s="1"/>
@@ -7670,6 +8375,8 @@
       <c r="Q192" s="1"/>
       <c r="R192" s="1"/>
       <c r="S192" s="1"/>
+      <c r="T192" s="1"/>
+      <c r="U192" s="1"/>
     </row>
     <row r="193">
       <c r="A193" s="1"/>
@@ -7691,6 +8398,8 @@
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
       <c r="S193" s="1"/>
+      <c r="T193" s="1"/>
+      <c r="U193" s="1"/>
     </row>
     <row r="194">
       <c r="A194" s="1"/>
@@ -7712,6 +8421,8 @@
       <c r="Q194" s="1"/>
       <c r="R194" s="1"/>
       <c r="S194" s="1"/>
+      <c r="T194" s="1"/>
+      <c r="U194" s="1"/>
     </row>
     <row r="195">
       <c r="A195" s="1"/>
@@ -7733,6 +8444,8 @@
       <c r="Q195" s="1"/>
       <c r="R195" s="1"/>
       <c r="S195" s="1"/>
+      <c r="T195" s="1"/>
+      <c r="U195" s="1"/>
     </row>
     <row r="196">
       <c r="A196" s="1"/>
@@ -7754,6 +8467,8 @@
       <c r="Q196" s="1"/>
       <c r="R196" s="1"/>
       <c r="S196" s="1"/>
+      <c r="T196" s="1"/>
+      <c r="U196" s="1"/>
     </row>
     <row r="197">
       <c r="A197" s="1"/>
@@ -7775,6 +8490,8 @@
       <c r="Q197" s="1"/>
       <c r="R197" s="1"/>
       <c r="S197" s="1"/>
+      <c r="T197" s="1"/>
+      <c r="U197" s="1"/>
     </row>
     <row r="198">
       <c r="A198" s="1"/>
@@ -7796,6 +8513,8 @@
       <c r="Q198" s="1"/>
       <c r="R198" s="1"/>
       <c r="S198" s="1"/>
+      <c r="T198" s="1"/>
+      <c r="U198" s="1"/>
     </row>
     <row r="199">
       <c r="A199" s="1"/>
@@ -7817,6 +8536,8 @@
       <c r="Q199" s="1"/>
       <c r="R199" s="1"/>
       <c r="S199" s="1"/>
+      <c r="T199" s="1"/>
+      <c r="U199" s="1"/>
     </row>
     <row r="200">
       <c r="A200" s="1"/>
@@ -7838,6 +8559,8 @@
       <c r="Q200" s="1"/>
       <c r="R200" s="1"/>
       <c r="S200" s="1"/>
+      <c r="T200" s="1"/>
+      <c r="U200" s="1"/>
     </row>
     <row r="201">
       <c r="A201" s="1"/>
@@ -7859,6 +8582,8 @@
       <c r="Q201" s="1"/>
       <c r="R201" s="1"/>
       <c r="S201" s="1"/>
+      <c r="T201" s="1"/>
+      <c r="U201" s="1"/>
     </row>
     <row r="202">
       <c r="A202" s="1"/>
@@ -7880,6 +8605,8 @@
       <c r="Q202" s="1"/>
       <c r="R202" s="1"/>
       <c r="S202" s="1"/>
+      <c r="T202" s="1"/>
+      <c r="U202" s="1"/>
     </row>
     <row r="203">
       <c r="A203" s="1"/>
@@ -7901,6 +8628,8 @@
       <c r="Q203" s="1"/>
       <c r="R203" s="1"/>
       <c r="S203" s="1"/>
+      <c r="T203" s="1"/>
+      <c r="U203" s="1"/>
     </row>
     <row r="204">
       <c r="A204" s="1"/>
@@ -7922,6 +8651,8 @@
       <c r="Q204" s="1"/>
       <c r="R204" s="1"/>
       <c r="S204" s="1"/>
+      <c r="T204" s="1"/>
+      <c r="U204" s="1"/>
     </row>
     <row r="205">
       <c r="A205" s="1"/>
@@ -7943,6 +8674,8 @@
       <c r="Q205" s="1"/>
       <c r="R205" s="1"/>
       <c r="S205" s="1"/>
+      <c r="T205" s="1"/>
+      <c r="U205" s="1"/>
     </row>
     <row r="206">
       <c r="A206" s="1"/>
@@ -7964,6 +8697,8 @@
       <c r="Q206" s="1"/>
       <c r="R206" s="1"/>
       <c r="S206" s="1"/>
+      <c r="T206" s="1"/>
+      <c r="U206" s="1"/>
     </row>
     <row r="207">
       <c r="A207" s="1"/>
@@ -7985,6 +8720,8 @@
       <c r="Q207" s="1"/>
       <c r="R207" s="1"/>
       <c r="S207" s="1"/>
+      <c r="T207" s="1"/>
+      <c r="U207" s="1"/>
     </row>
     <row r="208">
       <c r="A208" s="1"/>
@@ -8006,6 +8743,8 @@
       <c r="Q208" s="1"/>
       <c r="R208" s="1"/>
       <c r="S208" s="1"/>
+      <c r="T208" s="1"/>
+      <c r="U208" s="1"/>
     </row>
     <row r="209">
       <c r="A209" s="1"/>
@@ -8027,6 +8766,8 @@
       <c r="Q209" s="1"/>
       <c r="R209" s="1"/>
       <c r="S209" s="1"/>
+      <c r="T209" s="1"/>
+      <c r="U209" s="1"/>
     </row>
     <row r="210">
       <c r="A210" s="1"/>
@@ -8048,6 +8789,8 @@
       <c r="Q210" s="1"/>
       <c r="R210" s="1"/>
       <c r="S210" s="1"/>
+      <c r="T210" s="1"/>
+      <c r="U210" s="1"/>
     </row>
     <row r="211">
       <c r="A211" s="1"/>
@@ -8069,6 +8812,8 @@
       <c r="Q211" s="1"/>
       <c r="R211" s="1"/>
       <c r="S211" s="1"/>
+      <c r="T211" s="1"/>
+      <c r="U211" s="1"/>
     </row>
     <row r="212">
       <c r="A212" s="1"/>
@@ -8090,6 +8835,8 @@
       <c r="Q212" s="1"/>
       <c r="R212" s="1"/>
       <c r="S212" s="1"/>
+      <c r="T212" s="1"/>
+      <c r="U212" s="1"/>
     </row>
     <row r="213">
       <c r="A213" s="1"/>
@@ -8111,6 +8858,8 @@
       <c r="Q213" s="1"/>
       <c r="R213" s="1"/>
       <c r="S213" s="1"/>
+      <c r="T213" s="1"/>
+      <c r="U213" s="1"/>
     </row>
     <row r="214">
       <c r="A214" s="1"/>
@@ -8132,6 +8881,8 @@
       <c r="Q214" s="1"/>
       <c r="R214" s="1"/>
       <c r="S214" s="1"/>
+      <c r="T214" s="1"/>
+      <c r="U214" s="1"/>
     </row>
     <row r="215">
       <c r="A215" s="1"/>
@@ -8153,6 +8904,8 @@
       <c r="Q215" s="1"/>
       <c r="R215" s="1"/>
       <c r="S215" s="1"/>
+      <c r="T215" s="1"/>
+      <c r="U215" s="1"/>
     </row>
     <row r="216">
       <c r="A216" s="1"/>
@@ -8174,6 +8927,8 @@
       <c r="Q216" s="1"/>
       <c r="R216" s="1"/>
       <c r="S216" s="1"/>
+      <c r="T216" s="1"/>
+      <c r="U216" s="1"/>
     </row>
     <row r="217">
       <c r="A217" s="1"/>
@@ -8195,6 +8950,8 @@
       <c r="Q217" s="1"/>
       <c r="R217" s="1"/>
       <c r="S217" s="1"/>
+      <c r="T217" s="1"/>
+      <c r="U217" s="1"/>
     </row>
     <row r="218">
       <c r="A218" s="1"/>
@@ -8216,6 +8973,8 @@
       <c r="Q218" s="1"/>
       <c r="R218" s="1"/>
       <c r="S218" s="1"/>
+      <c r="T218" s="1"/>
+      <c r="U218" s="1"/>
     </row>
     <row r="219">
       <c r="A219" s="1"/>
@@ -8237,6 +8996,8 @@
       <c r="Q219" s="1"/>
       <c r="R219" s="1"/>
       <c r="S219" s="1"/>
+      <c r="T219" s="1"/>
+      <c r="U219" s="1"/>
     </row>
     <row r="220">
       <c r="A220" s="1"/>
@@ -8258,6 +9019,8 @@
       <c r="Q220" s="1"/>
       <c r="R220" s="1"/>
       <c r="S220" s="1"/>
+      <c r="T220" s="1"/>
+      <c r="U220" s="1"/>
     </row>
     <row r="221">
       <c r="A221" s="1"/>
@@ -8279,6 +9042,8 @@
       <c r="Q221" s="1"/>
       <c r="R221" s="1"/>
       <c r="S221" s="1"/>
+      <c r="T221" s="1"/>
+      <c r="U221" s="1"/>
     </row>
     <row r="222">
       <c r="A222" s="1"/>
@@ -8300,6 +9065,8 @@
       <c r="Q222" s="1"/>
       <c r="R222" s="1"/>
       <c r="S222" s="1"/>
+      <c r="T222" s="1"/>
+      <c r="U222" s="1"/>
     </row>
     <row r="223">
       <c r="A223" s="1"/>
@@ -8321,6 +9088,8 @@
       <c r="Q223" s="1"/>
       <c r="R223" s="1"/>
       <c r="S223" s="1"/>
+      <c r="T223" s="1"/>
+      <c r="U223" s="1"/>
     </row>
     <row r="224">
       <c r="A224" s="1"/>
@@ -8342,6 +9111,8 @@
       <c r="Q224" s="1"/>
       <c r="R224" s="1"/>
       <c r="S224" s="1"/>
+      <c r="T224" s="1"/>
+      <c r="U224" s="1"/>
     </row>
     <row r="225">
       <c r="A225" s="1"/>
@@ -8363,6 +9134,8 @@
       <c r="Q225" s="1"/>
       <c r="R225" s="1"/>
       <c r="S225" s="1"/>
+      <c r="T225" s="1"/>
+      <c r="U225" s="1"/>
     </row>
     <row r="226">
       <c r="A226" s="1"/>
@@ -8384,6 +9157,8 @@
       <c r="Q226" s="1"/>
       <c r="R226" s="1"/>
       <c r="S226" s="1"/>
+      <c r="T226" s="1"/>
+      <c r="U226" s="1"/>
     </row>
     <row r="227">
       <c r="A227" s="1"/>
@@ -8405,6 +9180,8 @@
       <c r="Q227" s="1"/>
       <c r="R227" s="1"/>
       <c r="S227" s="1"/>
+      <c r="T227" s="1"/>
+      <c r="U227" s="1"/>
     </row>
     <row r="228">
       <c r="A228" s="1"/>
@@ -8426,6 +9203,8 @@
       <c r="Q228" s="1"/>
       <c r="R228" s="1"/>
       <c r="S228" s="1"/>
+      <c r="T228" s="1"/>
+      <c r="U228" s="1"/>
     </row>
     <row r="229">
       <c r="A229" s="1"/>
@@ -8447,6 +9226,8 @@
       <c r="Q229" s="1"/>
       <c r="R229" s="1"/>
       <c r="S229" s="1"/>
+      <c r="T229" s="1"/>
+      <c r="U229" s="1"/>
     </row>
     <row r="230">
       <c r="A230" s="1"/>
@@ -8468,6 +9249,8 @@
       <c r="Q230" s="1"/>
       <c r="R230" s="1"/>
       <c r="S230" s="1"/>
+      <c r="T230" s="1"/>
+      <c r="U230" s="1"/>
     </row>
     <row r="231">
       <c r="A231" s="1"/>
@@ -8489,6 +9272,8 @@
       <c r="Q231" s="1"/>
       <c r="R231" s="1"/>
       <c r="S231" s="1"/>
+      <c r="T231" s="1"/>
+      <c r="U231" s="1"/>
     </row>
     <row r="232">
       <c r="A232" s="1"/>
@@ -8510,6 +9295,8 @@
       <c r="Q232" s="1"/>
       <c r="R232" s="1"/>
       <c r="S232" s="1"/>
+      <c r="T232" s="1"/>
+      <c r="U232" s="1"/>
     </row>
     <row r="233">
       <c r="A233" s="1"/>
@@ -8531,6 +9318,8 @@
       <c r="Q233" s="1"/>
       <c r="R233" s="1"/>
       <c r="S233" s="1"/>
+      <c r="T233" s="1"/>
+      <c r="U233" s="1"/>
     </row>
     <row r="234">
       <c r="A234" s="1"/>
@@ -8552,6 +9341,8 @@
       <c r="Q234" s="1"/>
       <c r="R234" s="1"/>
       <c r="S234" s="1"/>
+      <c r="T234" s="1"/>
+      <c r="U234" s="1"/>
     </row>
     <row r="235">
       <c r="A235" s="1"/>
@@ -8573,6 +9364,8 @@
       <c r="Q235" s="1"/>
       <c r="R235" s="1"/>
       <c r="S235" s="1"/>
+      <c r="T235" s="1"/>
+      <c r="U235" s="1"/>
     </row>
     <row r="236">
       <c r="A236" s="1"/>
@@ -8594,6 +9387,8 @@
       <c r="Q236" s="1"/>
       <c r="R236" s="1"/>
       <c r="S236" s="1"/>
+      <c r="T236" s="1"/>
+      <c r="U236" s="1"/>
     </row>
     <row r="237">
       <c r="A237" s="1"/>
@@ -8615,6 +9410,8 @@
       <c r="Q237" s="1"/>
       <c r="R237" s="1"/>
       <c r="S237" s="1"/>
+      <c r="T237" s="1"/>
+      <c r="U237" s="1"/>
     </row>
     <row r="238">
       <c r="A238" s="1"/>
@@ -8636,6 +9433,8 @@
       <c r="Q238" s="1"/>
       <c r="R238" s="1"/>
       <c r="S238" s="1"/>
+      <c r="T238" s="1"/>
+      <c r="U238" s="1"/>
     </row>
     <row r="239">
       <c r="A239" s="1"/>
@@ -8657,6 +9456,8 @@
       <c r="Q239" s="1"/>
       <c r="R239" s="1"/>
       <c r="S239" s="1"/>
+      <c r="T239" s="1"/>
+      <c r="U239" s="1"/>
     </row>
     <row r="240">
       <c r="A240" s="1"/>
@@ -8678,6 +9479,8 @@
       <c r="Q240" s="1"/>
       <c r="R240" s="1"/>
       <c r="S240" s="1"/>
+      <c r="T240" s="1"/>
+      <c r="U240" s="1"/>
     </row>
     <row r="241">
       <c r="A241" s="1"/>
@@ -8699,6 +9502,8 @@
       <c r="Q241" s="1"/>
       <c r="R241" s="1"/>
       <c r="S241" s="1"/>
+      <c r="T241" s="1"/>
+      <c r="U241" s="1"/>
     </row>
     <row r="242">
       <c r="A242" s="1"/>
@@ -8720,6 +9525,8 @@
       <c r="Q242" s="1"/>
       <c r="R242" s="1"/>
       <c r="S242" s="1"/>
+      <c r="T242" s="1"/>
+      <c r="U242" s="1"/>
     </row>
     <row r="243">
       <c r="A243" s="1"/>
@@ -8741,6 +9548,8 @@
       <c r="Q243" s="1"/>
       <c r="R243" s="1"/>
       <c r="S243" s="1"/>
+      <c r="T243" s="1"/>
+      <c r="U243" s="1"/>
     </row>
     <row r="244">
       <c r="A244" s="1"/>
@@ -8762,6 +9571,8 @@
       <c r="Q244" s="1"/>
       <c r="R244" s="1"/>
       <c r="S244" s="1"/>
+      <c r="T244" s="1"/>
+      <c r="U244" s="1"/>
     </row>
     <row r="245">
       <c r="A245" s="1"/>
@@ -8783,6 +9594,8 @@
       <c r="Q245" s="1"/>
       <c r="R245" s="1"/>
       <c r="S245" s="1"/>
+      <c r="T245" s="1"/>
+      <c r="U245" s="1"/>
     </row>
     <row r="246">
       <c r="A246" s="1"/>
@@ -8804,6 +9617,8 @@
       <c r="Q246" s="1"/>
       <c r="R246" s="1"/>
       <c r="S246" s="1"/>
+      <c r="T246" s="1"/>
+      <c r="U246" s="1"/>
     </row>
     <row r="247">
       <c r="A247" s="1"/>
@@ -8825,6 +9640,8 @@
       <c r="Q247" s="1"/>
       <c r="R247" s="1"/>
       <c r="S247" s="1"/>
+      <c r="T247" s="1"/>
+      <c r="U247" s="1"/>
     </row>
     <row r="248">
       <c r="A248" s="1"/>
@@ -8846,6 +9663,8 @@
       <c r="Q248" s="1"/>
       <c r="R248" s="1"/>
       <c r="S248" s="1"/>
+      <c r="T248" s="1"/>
+      <c r="U248" s="1"/>
     </row>
     <row r="249">
       <c r="A249" s="1"/>
@@ -8867,6 +9686,8 @@
       <c r="Q249" s="1"/>
       <c r="R249" s="1"/>
       <c r="S249" s="1"/>
+      <c r="T249" s="1"/>
+      <c r="U249" s="1"/>
     </row>
     <row r="250">
       <c r="A250" s="1"/>
@@ -8888,6 +9709,8 @@
       <c r="Q250" s="1"/>
       <c r="R250" s="1"/>
       <c r="S250" s="1"/>
+      <c r="T250" s="1"/>
+      <c r="U250" s="1"/>
     </row>
     <row r="251">
       <c r="A251" s="1"/>
@@ -8909,6 +9732,8 @@
       <c r="Q251" s="1"/>
       <c r="R251" s="1"/>
       <c r="S251" s="1"/>
+      <c r="T251" s="1"/>
+      <c r="U251" s="1"/>
     </row>
     <row r="252">
       <c r="A252" s="1"/>
@@ -8930,6 +9755,8 @@
       <c r="Q252" s="1"/>
       <c r="R252" s="1"/>
       <c r="S252" s="1"/>
+      <c r="T252" s="1"/>
+      <c r="U252" s="1"/>
     </row>
     <row r="253">
       <c r="A253" s="1"/>
@@ -8951,6 +9778,8 @@
       <c r="Q253" s="1"/>
       <c r="R253" s="1"/>
       <c r="S253" s="1"/>
+      <c r="T253" s="1"/>
+      <c r="U253" s="1"/>
     </row>
     <row r="254">
       <c r="A254" s="1"/>
@@ -8972,6 +9801,8 @@
       <c r="Q254" s="1"/>
       <c r="R254" s="1"/>
       <c r="S254" s="1"/>
+      <c r="T254" s="1"/>
+      <c r="U254" s="1"/>
     </row>
     <row r="255">
       <c r="A255" s="1"/>
@@ -8993,6 +9824,8 @@
       <c r="Q255" s="1"/>
       <c r="R255" s="1"/>
       <c r="S255" s="1"/>
+      <c r="T255" s="1"/>
+      <c r="U255" s="1"/>
     </row>
     <row r="256">
       <c r="A256" s="1"/>
@@ -9014,6 +9847,8 @@
       <c r="Q256" s="1"/>
       <c r="R256" s="1"/>
       <c r="S256" s="1"/>
+      <c r="T256" s="1"/>
+      <c r="U256" s="1"/>
     </row>
     <row r="257">
       <c r="A257" s="1"/>
@@ -9035,6 +9870,8 @@
       <c r="Q257" s="1"/>
       <c r="R257" s="1"/>
       <c r="S257" s="1"/>
+      <c r="T257" s="1"/>
+      <c r="U257" s="1"/>
     </row>
     <row r="258">
       <c r="A258" s="1"/>
@@ -9056,6 +9893,8 @@
       <c r="Q258" s="1"/>
       <c r="R258" s="1"/>
       <c r="S258" s="1"/>
+      <c r="T258" s="1"/>
+      <c r="U258" s="1"/>
     </row>
     <row r="259">
       <c r="A259" s="1"/>
@@ -9077,6 +9916,8 @@
       <c r="Q259" s="1"/>
       <c r="R259" s="1"/>
       <c r="S259" s="1"/>
+      <c r="T259" s="1"/>
+      <c r="U259" s="1"/>
     </row>
     <row r="260">
       <c r="A260" s="1"/>
@@ -9098,6 +9939,8 @@
       <c r="Q260" s="1"/>
       <c r="R260" s="1"/>
       <c r="S260" s="1"/>
+      <c r="T260" s="1"/>
+      <c r="U260" s="1"/>
     </row>
     <row r="261">
       <c r="A261" s="1"/>
@@ -9119,6 +9962,8 @@
       <c r="Q261" s="1"/>
       <c r="R261" s="1"/>
       <c r="S261" s="1"/>
+      <c r="T261" s="1"/>
+      <c r="U261" s="1"/>
     </row>
     <row r="262">
       <c r="A262" s="1"/>
@@ -9140,6 +9985,8 @@
       <c r="Q262" s="1"/>
       <c r="R262" s="1"/>
       <c r="S262" s="1"/>
+      <c r="T262" s="1"/>
+      <c r="U262" s="1"/>
     </row>
     <row r="263">
       <c r="A263" s="1"/>
@@ -9161,6 +10008,8 @@
       <c r="Q263" s="1"/>
       <c r="R263" s="1"/>
       <c r="S263" s="1"/>
+      <c r="T263" s="1"/>
+      <c r="U263" s="1"/>
     </row>
     <row r="264">
       <c r="A264" s="1"/>
@@ -9182,6 +10031,8 @@
       <c r="Q264" s="1"/>
       <c r="R264" s="1"/>
       <c r="S264" s="1"/>
+      <c r="T264" s="1"/>
+      <c r="U264" s="1"/>
     </row>
     <row r="265">
       <c r="A265" s="1"/>
@@ -9203,6 +10054,8 @@
       <c r="Q265" s="1"/>
       <c r="R265" s="1"/>
       <c r="S265" s="1"/>
+      <c r="T265" s="1"/>
+      <c r="U265" s="1"/>
     </row>
     <row r="266">
       <c r="A266" s="1"/>
@@ -9224,6 +10077,8 @@
       <c r="Q266" s="1"/>
       <c r="R266" s="1"/>
       <c r="S266" s="1"/>
+      <c r="T266" s="1"/>
+      <c r="U266" s="1"/>
     </row>
     <row r="267">
       <c r="A267" s="1"/>
@@ -9245,6 +10100,8 @@
       <c r="Q267" s="1"/>
       <c r="R267" s="1"/>
       <c r="S267" s="1"/>
+      <c r="T267" s="1"/>
+      <c r="U267" s="1"/>
     </row>
     <row r="268">
       <c r="A268" s="1"/>
@@ -9266,6 +10123,8 @@
       <c r="Q268" s="1"/>
       <c r="R268" s="1"/>
       <c r="S268" s="1"/>
+      <c r="T268" s="1"/>
+      <c r="U268" s="1"/>
     </row>
     <row r="269">
       <c r="A269" s="1"/>
@@ -9287,6 +10146,8 @@
       <c r="Q269" s="1"/>
       <c r="R269" s="1"/>
       <c r="S269" s="1"/>
+      <c r="T269" s="1"/>
+      <c r="U269" s="1"/>
     </row>
     <row r="270">
       <c r="A270" s="1"/>
@@ -9308,6 +10169,8 @@
       <c r="Q270" s="1"/>
       <c r="R270" s="1"/>
       <c r="S270" s="1"/>
+      <c r="T270" s="1"/>
+      <c r="U270" s="1"/>
     </row>
     <row r="271">
       <c r="A271" s="1"/>
@@ -9329,6 +10192,8 @@
       <c r="Q271" s="1"/>
       <c r="R271" s="1"/>
       <c r="S271" s="1"/>
+      <c r="T271" s="1"/>
+      <c r="U271" s="1"/>
     </row>
     <row r="272">
       <c r="A272" s="1"/>
@@ -9350,6 +10215,8 @@
       <c r="Q272" s="1"/>
       <c r="R272" s="1"/>
       <c r="S272" s="1"/>
+      <c r="T272" s="1"/>
+      <c r="U272" s="1"/>
     </row>
     <row r="273">
       <c r="A273" s="1"/>
@@ -9371,6 +10238,8 @@
       <c r="Q273" s="1"/>
       <c r="R273" s="1"/>
       <c r="S273" s="1"/>
+      <c r="T273" s="1"/>
+      <c r="U273" s="1"/>
     </row>
     <row r="274">
       <c r="A274" s="1"/>
@@ -9392,6 +10261,8 @@
       <c r="Q274" s="1"/>
       <c r="R274" s="1"/>
       <c r="S274" s="1"/>
+      <c r="T274" s="1"/>
+      <c r="U274" s="1"/>
     </row>
     <row r="275">
       <c r="A275" s="1"/>
@@ -9413,6 +10284,8 @@
       <c r="Q275" s="1"/>
       <c r="R275" s="1"/>
       <c r="S275" s="1"/>
+      <c r="T275" s="1"/>
+      <c r="U275" s="1"/>
     </row>
     <row r="276">
       <c r="A276" s="1"/>
@@ -9434,6 +10307,8 @@
       <c r="Q276" s="1"/>
       <c r="R276" s="1"/>
       <c r="S276" s="1"/>
+      <c r="T276" s="1"/>
+      <c r="U276" s="1"/>
     </row>
     <row r="277">
       <c r="A277" s="1"/>
@@ -9455,6 +10330,8 @@
       <c r="Q277" s="1"/>
       <c r="R277" s="1"/>
       <c r="S277" s="1"/>
+      <c r="T277" s="1"/>
+      <c r="U277" s="1"/>
     </row>
     <row r="278">
       <c r="A278" s="1"/>
@@ -9476,9 +10353,11 @@
       <c r="Q278" s="1"/>
       <c r="R278" s="1"/>
       <c r="S278" s="1"/>
+      <c r="T278" s="1"/>
+      <c r="U278" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S78"/>
+  <autoFilter ref="A1:U78"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
